--- a/output/2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx
+++ b/output/2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
